--- a/RacePromo.xlsx
+++ b/RacePromo.xlsx
@@ -4,6 +4,7 @@
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
     <sheet name="Race_Promo_Calendar" sheetId="2" r:id="rId2"/>
+    <sheet name="Race_Naming_Calendar" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -47,14 +48,12 @@
   </fills>
   <borders count="9">
     <border>
-      <left style="thin">
+      <left/>
+      <right style="thin">
         <color indexed="64"/>
-      </left>
-      <right/>
+      </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -80,12 +79,14 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
+      <left style="thin">
         <color indexed="64"/>
-      </right>
+      </left>
+      <right/>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1034,7 +1035,7 @@
           <t xml:space="preserve">Title</t>
         </is>
       </c>
-      <c r="B2" s="75" t="inlineStr">
+      <c r="B2" s="72" t="inlineStr">
         <is>
           <t xml:space="preserve">Race Promotion Summary 2025-2028</t>
         </is>
@@ -1046,7 +1047,7 @@
           <t xml:space="preserve">Source</t>
         </is>
       </c>
-      <c r="B3" s="75" t="inlineStr">
+      <c r="B3" s="72" t="inlineStr">
         <is>
           <t xml:space="preserve">F1 Race promotions.xlsx (sole workbook source)</t>
         </is>
@@ -1058,7 +1059,7 @@
           <t xml:space="preserve">Calendar</t>
         </is>
       </c>
-      <c r="B4" s="75" t="inlineStr">
+      <c r="B4" s="72" t="inlineStr">
         <is>
           <t xml:space="preserve">FIA/F1 official 2026 and 2027 calendars</t>
         </is>
@@ -1070,7 +1071,7 @@
           <t xml:space="preserve">As Of</t>
         </is>
       </c>
-      <c r="B5" s="75" t="inlineStr">
+      <c r="B5" s="72" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-27</t>
         </is>
@@ -1082,14 +1083,14 @@
           <t xml:space="preserve">Units</t>
         </is>
       </c>
-      <c r="B6" s="75" t="inlineStr">
+      <c r="B6" s="72" t="inlineStr">
         <is>
           <t xml:space="preserve">USD millions</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Created</t>
         </is>
@@ -1120,6 +1121,8 @@
     <col min="11" max="11" width="58.00" customWidth="1"/>
     <col min="12" max="12" width="70.00" customWidth="1"/>
     <col min="13" max="13" width="60.00" customWidth="1"/>
+    <col min="14" max="14" width="9.00" customWidth="1"/>
+    <col min="15" max="15" width="9.00" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1188,6 +1191,16 @@
           <t xml:space="preserve">Sources</t>
         </is>
       </c>
+      <c r="N1" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Start Year</t>
+        </is>
+      </c>
+      <c r="O1" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">End Year</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
@@ -1238,7 +1251,7 @@
           <t xml:space="preserve">Two model revisions cut the fee from $40M to $35M after the AR1 $40M print was judged an uplift; PlanetF1's $48.1M 2026 figure is total F1 event cost including F2/F3, not the pure fee. The fee is FOI-blocked, so every number is press-derived.</t>
         </is>
       </c>
-      <c r="M2" s="30" t="inlineStr">
+      <c r="M2" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://racingnews365.com/f1-2025-circuit-contracts
 https://www.autoracing1.com/pl/419102/formula-1-news-japanese-gp-gets-5-year-extension/
@@ -1249,6 +1262,12 @@
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2027-season-with-10-sprint-events.5J8ePLyjRuMyWEIDNUKgY4</t>
         </is>
       </c>
+      <c r="N2" s="150">
+        <v>2025</v>
+      </c>
+      <c r="O2" s="150">
+        <v>2037</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
@@ -1299,7 +1318,7 @@
           <t xml:space="preserve">Held at $50M (RN365) after a $58M East-Asia premium was unwound; a 2024-2030 extension is confirmed but F1 has not published a fee. One of the few rows where the model removed its own uplift.</t>
         </is>
       </c>
-      <c r="M3" s="30" t="inlineStr">
+      <c r="M3" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://racingnews365.com/f1-2025-circuit-contracts
 https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar
@@ -1307,6 +1326,12 @@
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2027-season-with-10-sprint-events.5J8ePLyjRuMyWEIDNUKgY4</t>
         </is>
       </c>
+      <c r="N3" s="150">
+        <v>2025</v>
+      </c>
+      <c r="O3" s="150">
+        <v>2030</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -1357,7 +1382,7 @@
           <t xml:space="preserve">The widest range in the file: RN365's grid still shows ~$25M while AR1 assumes ~$50M for the 2024-29 renewal. The model settled on $30M TRADE and labels the $50M unconfirmed — a ~$25M swing on one race.</t>
         </is>
       </c>
-      <c r="M4" s="30" t="inlineStr">
+      <c r="M4" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.autoracing1.com/pl/419102/formula-1-news-japanese-gp-gets-5-year-extension/
 https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar
@@ -1365,6 +1390,12 @@
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2027-season-with-10-sprint-events.5J8ePLyjRuMyWEIDNUKgY4</t>
         </is>
       </c>
+      <c r="N4" s="150">
+        <v>2025</v>
+      </c>
+      <c r="O4" s="150">
+        <v>2029</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -1396,10 +1427,10 @@
       <c r="G5" s="240">
         <v>55</v>
       </c>
-      <c r="H5" s="240"/>
-      <c r="I5" s="240">
+      <c r="H5" s="240">
         <v>60.64</v>
       </c>
+      <c r="I5" s="240"/>
       <c r="J5" s="240">
         <v>63.67</v>
       </c>
@@ -1413,13 +1444,19 @@
           <t xml:space="preserve">Carries the Bahrain fee from 2022 to 2036, with FY26 blank because the 2026 venue was Sepang. Guggenheim's ~$115M combined Bahrain+Saudi print brackets the pair at $55M + $60M.</t>
         </is>
       </c>
-      <c r="M5" s="30" t="inlineStr">
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.sportico.com/leagues/motorsports/2026/how-f1s-middle-east-woes-could-hurt-revenue-promoter-fees-1234887237/
 https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2026-season.YctbMZWqBvrgyddrnauo8</t>
         </is>
       </c>
+      <c r="N5" s="150">
+        <v>2022</v>
+      </c>
+      <c r="O5" s="150">
+        <v>2036</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
@@ -1470,7 +1507,7 @@
           <t xml:space="preserve">Priced at $60M as the residual of Guggenheim's ~$115M Bahrain+Saudi pair; buy-side notes put Saudi in the low-$60s with ~5% annual step-up. A move to Qiddiya around 2028 is flagged as possible.</t>
         </is>
       </c>
-      <c r="M6" s="30" t="inlineStr">
+      <c r="M6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.sportico.com/leagues/motorsports/2026/how-f1s-middle-east-woes-could-hurt-revenue-promoter-fees-1234887237/
 https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar
@@ -1478,6 +1515,12 @@
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2027-season-with-10-sprint-events.5J8ePLyjRuMyWEIDNUKgY4</t>
         </is>
       </c>
+      <c r="N6" s="150">
+        <v>2021</v>
+      </c>
+      <c r="O6" s="150">
+        <v>2030</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
@@ -1510,23 +1553,25 @@
       <c r="H7" s="240"/>
       <c r="I7" s="240"/>
       <c r="J7" s="240"/>
-      <c r="K7" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No promotion fee is disclosed. Miami runs under a revenue-sharing collaboration with South Florida Motorsports rather than a flat sanction fee, so Liberty takes a share of race economics instead of a promoter payment.</t>
-        </is>
-      </c>
+      <c r="K7" s="33"/>
       <c r="L7" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">The only race with a blank fee: it is a collaboration/co-promote with South Florida Motorsports, not a flat F1 sanction, so Liberty's revenue share is undisclosed in the 10-K. Contract runs to 2041.</t>
         </is>
       </c>
-      <c r="M7" s="30" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2026-season.YctbMZWqBvrgyddrnauo8
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2027-season-with-10-sprint-events.5J8ePLyjRuMyWEIDNUKgY4</t>
         </is>
       </c>
+      <c r="N7" s="150">
+        <v>2022</v>
+      </c>
+      <c r="O7" s="150">
+        <v>2041</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
@@ -1577,7 +1622,7 @@
           <t xml:space="preserve">Journal de Montréal brackets the fee at $26M in 2031 rising to ~$29M for 2032-35, which is why FY25-FY28 (~$25-29M) sit below the $30M AAV. A C$117M public pledge is co-funding, not the F1 invoice.</t>
         </is>
       </c>
-      <c r="M8" s="30" t="inlineStr">
+      <c r="M8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://motorsport.nextgen-auto.com/en/formula-1/montreal-accepts-3m-fee-hike-to-keep-f1-race
 https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar
@@ -1585,6 +1630,12 @@
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2027-season-with-10-sprint-events.5J8ePLyjRuMyWEIDNUKgY4</t>
         </is>
       </c>
+      <c r="N8" s="150">
+        <v>2025</v>
+      </c>
+      <c r="O8" s="150">
+        <v>2035</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -1635,7 +1686,7 @@
           <t xml:space="preserve">The 2024 renewal doubled the fee from ~€12M/$15M to £25M (~$32M), later extended to 2035. One buy-side note still models mid-teens $M, which the file flags as a pre-doubling estimate.</t>
         </is>
       </c>
-      <c r="M9" s="30" t="inlineStr">
+      <c r="M9" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://racingnews365.com/monaco-gp-signs-new-long-term-deal-with-f1
 https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar
@@ -1643,6 +1694,12 @@
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2027-season-with-10-sprint-events.5J8ePLyjRuMyWEIDNUKgY4</t>
         </is>
       </c>
+      <c r="N9" s="150">
+        <v>2026</v>
+      </c>
+      <c r="O9" s="150">
+        <v>2035</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -1664,11 +1721,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="150"/>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HARD</t>
-        </is>
-      </c>
+      <c r="F10" s="6"/>
       <c r="G10" s="240">
         <v>28</v>
       </c>
@@ -1691,12 +1744,18 @@
           <t xml:space="preserve">The only European race on a 3% escalator: Spain's BOE guarantee schedule ($25/25.5/26.5/28M for 2023-26) is treated as the contractual fee. Drops off after 2026 in favour of Madrid, with even-year rotation possible.</t>
         </is>
       </c>
-      <c r="M10" s="30" t="inlineStr">
+      <c r="M10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2026-season.YctbMZWqBvrgyddrnauo8</t>
         </is>
       </c>
+      <c r="N10" s="150">
+        <v>2023</v>
+      </c>
+      <c r="O10" s="150">
+        <v>2032</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -1747,7 +1806,7 @@
           <t xml:space="preserve">Cheap versus peers at $25M, and the file notes AR1 expects a step to ~$30M from 2030 on the deal running to 2041. That step is flagged as not modelled in the 2025-28 curve.</t>
         </is>
       </c>
-      <c r="M11" s="30" t="inlineStr">
+      <c r="M11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://racingnews365.com/f1-2025-circuit-contracts
 https://www.autoracing1.com/pl/453817/formula-1-news-f1-event-statistics-after-renewal-of-austrian-gp/
@@ -1756,6 +1815,12 @@
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2027-season-with-10-sprint-events.5J8ePLyjRuMyWEIDNUKgY4</t>
         </is>
       </c>
+      <c r="N11" s="150">
+        <v>2025</v>
+      </c>
+      <c r="O11" s="150">
+        <v>2041</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
@@ -1806,7 +1871,7 @@
           <t xml:space="preserve">Fee raised from $25M to $38M using the £30M/yr print (~£300M over 10 years to 2034). Privately funded by the BRDC with no UK government hosting subsidy.</t>
         </is>
       </c>
-      <c r="M12" s="30" t="inlineStr">
+      <c r="M12" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.planetf1.com/news/british-gp-silverstone-new-deal-signed
 https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar
@@ -1814,6 +1879,12 @@
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2027-season-with-10-sprint-events.5J8ePLyjRuMyWEIDNUKgY4</t>
         </is>
       </c>
+      <c r="N12" s="150">
+        <v>2025</v>
+      </c>
+      <c r="O12" s="150">
+        <v>2034</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
@@ -1852,17 +1923,13 @@
         <v>33.08</v>
       </c>
       <c r="J13" s="240"/>
-      <c r="K13" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fee of about EUR 28M ($30M) per year under the Walloon government contract. The race moves to alternate-year hosting from 2027.</t>
-        </is>
-      </c>
+      <c r="K13" s="33"/>
       <c r="L13" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Wallonia's parliamentary print of €28M for 2025 underpins $30M, well above RN365's ~$25M. Moves to odd-year rotation from 2027, alternating with Barcelona.</t>
         </is>
       </c>
-      <c r="M13" s="30" t="inlineStr">
+      <c r="M13" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.rtbf.be/article/f1-accueillir-le-grand-prix-de-belgique-vitrine-essentielle-de-la-wallonie-coute-de-plus-en-plus-cher-11321065
 https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar
@@ -1870,6 +1937,12 @@
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2027-season-with-10-sprint-events.5J8ePLyjRuMyWEIDNUKgY4</t>
         </is>
       </c>
+      <c r="N13" s="150">
+        <v>2026</v>
+      </c>
+      <c r="O13" s="150">
+        <v>2031</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -1920,7 +1993,7 @@
           <t xml:space="preserve">The hardest number in the file: the Hungarian government gazette sets the 2024 fee at exactly $49,684,662.80 with a 2% escalator. Management separately claims the deal saves $61.7M, and public ~$40M estimates sit below the gazette figure.</t>
         </is>
       </c>
-      <c r="M14" s="30" t="inlineStr">
+      <c r="M14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://telex.hu/g7/vallalat/2026/07/24/hungaroring-jogdij-ertekesites-ostermann-felujitas-koltsegek-gyulay
 https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar
@@ -1928,6 +2001,12 @@
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2027-season-with-10-sprint-events.5J8ePLyjRuMyWEIDNUKgY4</t>
         </is>
       </c>
+      <c r="N14" s="150">
+        <v>2028</v>
+      </c>
+      <c r="O14" s="150">
+        <v>2032</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
@@ -1949,11 +2028,7 @@
         <v>14</v>
       </c>
       <c r="E15" s="150"/>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRADE</t>
-        </is>
-      </c>
+      <c r="F15" s="6"/>
       <c r="G15" s="240">
         <v>35</v>
       </c>
@@ -1962,23 +2037,25 @@
       </c>
       <c r="I15" s="240"/>
       <c r="J15" s="240"/>
-      <c r="K15" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fee of about $35M per year under the contract, which ends with the 2026 race.</t>
-        </is>
-      </c>
+      <c r="K15" s="33"/>
       <c r="L15" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Final contracted year is 2026 and it is absent from the published 2027 calendar. Privately funded with no central Dutch subsidy; the promoter's €70-75M weekend budget is not the fee.</t>
         </is>
       </c>
-      <c r="M15" s="30" t="inlineStr">
+      <c r="M15" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://racingnews365.com/f1-2025-circuit-contracts
 https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2026-season.YctbMZWqBvrgyddrnauo8</t>
         </is>
       </c>
+      <c r="N15" s="150">
+        <v>2021</v>
+      </c>
+      <c r="O15" s="150">
+        <v>2026</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -2029,7 +2106,7 @@
           <t xml:space="preserve">Fee lifted to $32M on the post-2024 six-year renewal (~€30M). An Italian court filing showing €17.6M relates to the old contract and is excluded from the 2025+ curve.</t>
         </is>
       </c>
-      <c r="M16" s="30" t="inlineStr">
+      <c r="M16" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.autoracing1.com/pl/438387/f1-news-f1-event-statistics-with-italian-gp-after-monza-renewal/
 https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar
@@ -2037,6 +2114,12 @@
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2027-season-with-10-sprint-events.5J8ePLyjRuMyWEIDNUKgY4</t>
         </is>
       </c>
+      <c r="N16" s="150">
+        <v>2026</v>
+      </c>
+      <c r="O16" s="150">
+        <v>2031</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
@@ -2065,10 +2148,10 @@
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G17" s="240"/>
-      <c r="H17" s="240">
+      <c r="G17" s="240">
         <v>41.75</v>
       </c>
+      <c r="H17" s="240"/>
       <c r="I17" s="240">
         <v>43.84</v>
       </c>
@@ -2085,7 +2168,7 @@
           <t xml:space="preserve">New from 2026 on a 10-year IFEMA deal at ~€48M/yr (~$52M), close to double Catalunya's ~€26M — the price of the Spanish slot roughly doubled. Fee still officially undisclosed as of mid-2026.</t>
         </is>
       </c>
-      <c r="M17" s="30" t="inlineStr">
+      <c r="M17" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.3cat.cat/3catinfo/madrid-pagara-a-la-formula-1-gairebe-el-doble-que-catalunya-500-milions-en-deu-anys/noticia/3272590/
 https://www.planetf1.com/features/imola-f1-future-calendar-21-million-emilia-romagna-grand-prix
@@ -2094,6 +2177,12 @@
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2027-season-with-10-sprint-events.5J8ePLyjRuMyWEIDNUKgY4</t>
         </is>
       </c>
+      <c r="N17" s="150">
+        <v>2026</v>
+      </c>
+      <c r="O17" s="150">
+        <v>2035</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
@@ -2144,7 +2233,7 @@
           <t xml:space="preserve">Held at $55M after a $57M uplift was reverted; a four-year extension to 2030 was signed in 2025. Sits in the same $50-60M MENA/Caucasus band as the Gulf races.</t>
         </is>
       </c>
-      <c r="M18" s="30" t="inlineStr">
+      <c r="M18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://speedcafe.com/f1-race-fees-reveal-bargain-australian-gp/
 https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar
@@ -2152,6 +2241,12 @@
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2027-season-with-10-sprint-events.5J8ePLyjRuMyWEIDNUKgY4</t>
         </is>
       </c>
+      <c r="N18" s="150">
+        <v>2027</v>
+      </c>
+      <c r="O18" s="150">
+        <v>2030</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
@@ -2202,7 +2297,7 @@
           <t xml:space="preserve">Fee is confidential and the government funds ~60% of a ~S$140M/yr organising cost — that envelope is not the F1 fee. Model cut the fee from $48M back to $35M (RN365).</t>
         </is>
       </c>
-      <c r="M19" s="30" t="inlineStr">
+      <c r="M19" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://racingnews365.com/f1-2025-circuit-contracts
 https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar
@@ -2210,6 +2305,12 @@
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2027-season-with-10-sprint-events.5J8ePLyjRuMyWEIDNUKgY4</t>
         </is>
       </c>
+      <c r="N19" s="150">
+        <v>2022</v>
+      </c>
+      <c r="O19" s="150">
+        <v>2028</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
@@ -2260,7 +2361,7 @@
           <t xml:space="preserve">Raised from $25M to $30M on Speedcafe's print; PlanetF1 puts the pass-mark for an existing US race at ~$35M. Extension to 2034 announced in 2025.</t>
         </is>
       </c>
-      <c r="M20" s="30" t="inlineStr">
+      <c r="M20" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://speedcafe.com/f1-race-fees-reveal-bargain-australian-gp/
 https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar
@@ -2268,6 +2369,12 @@
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2027-season-with-10-sprint-events.5J8ePLyjRuMyWEIDNUKgY4</t>
         </is>
       </c>
+      <c r="N20" s="150">
+        <v>2026</v>
+      </c>
+      <c r="O20" s="150">
+        <v>2034</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
@@ -2318,7 +2425,7 @@
           <t xml:space="preserve">Moved from $25M to $40M on the CIE CEO's statement that industry fees now run $40-70M and Mexico pays roughly average. An earlier $55M mid-band figure was walked back as too high.</t>
         </is>
       </c>
-      <c r="M21" s="30" t="inlineStr">
+      <c r="M21" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.eleconomista.com.mx/deportes/gran-premio-cdmx-busca-volverse-sostenible-20241028-731917.html
 https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar
@@ -2326,6 +2433,12 @@
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2027-season-with-10-sprint-events.5J8ePLyjRuMyWEIDNUKgY4</t>
         </is>
       </c>
+      <c r="N21" s="150">
+        <v>2026</v>
+      </c>
+      <c r="O21" s="150">
+        <v>2028</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
@@ -2376,7 +2489,7 @@
           <t xml:space="preserve">Effectively disclosed: Mayor Nunes put the fee at US$125M for the first five years (~$25M/yr), replicated through 2030. A separate R$100M payment to Mubadala is organising cost, not the F1 fee.</t>
         </is>
       </c>
-      <c r="M22" s="30" t="inlineStr">
+      <c r="M22" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.estadao.com.br/esportes/velocidade/f1-sao-paulo-gp-2030-autodromo-interlagos-npres/
 https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar
@@ -2384,6 +2497,12 @@
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2027-season-with-10-sprint-events.5J8ePLyjRuMyWEIDNUKgY4</t>
         </is>
       </c>
+      <c r="N22" s="150">
+        <v>2023</v>
+      </c>
+      <c r="O22" s="150">
+        <v>2030</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
@@ -2434,13 +2553,19 @@
           <t xml:space="preserve">Not a promoter fee at all. Liberty promotes the race directly, so the $210M is consolidated grandstand and general-admission ticketing; hospitality and sponsorship sit in other revenue lines.</t>
         </is>
       </c>
-      <c r="M23" s="30" t="inlineStr">
+      <c r="M23" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2026-season.YctbMZWqBvrgyddrnauo8
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2027-season-with-10-sprint-events.5J8ePLyjRuMyWEIDNUKgY4</t>
         </is>
       </c>
+      <c r="N23" s="150">
+        <v>2023</v>
+      </c>
+      <c r="O23" s="150">
+        <v>2037</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
@@ -2491,7 +2616,7 @@
           <t xml:space="preserve">In the $50-60M Gulf band at $55M, but the file records a direct conflict: one buy-side note puts Qatar race promotion in the high-teens $M while another calls it a large race-promo race. The gap is flagged, not resolved.</t>
         </is>
       </c>
-      <c r="M24" s="30" t="inlineStr">
+      <c r="M24" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://racingnews365.com/f1-2025-circuit-contracts
 https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar
@@ -2499,6 +2624,12 @@
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2027-season-with-10-sprint-events.5J8ePLyjRuMyWEIDNUKgY4</t>
         </is>
       </c>
+      <c r="N24" s="150">
+        <v>2023</v>
+      </c>
+      <c r="O24" s="150">
+        <v>2032</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
@@ -2549,13 +2680,19 @@
           <t xml:space="preserve">Revised three times ($40M to $55M to $42M) as the model oscillated between RN365/Speedcafe prints and a Gulf $50-60M band. Company commentary describes it as a large race-promotion race.</t>
         </is>
       </c>
-      <c r="M25" s="30" t="inlineStr">
+      <c r="M25" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2026-season.YctbMZWqBvrgyddrnauo8
 https://www.formula1.com/en/latest/article/formula-1-reveals-calendar-for-2027-season-with-10-sprint-events.5J8ePLyjRuMyWEIDNUKgY4</t>
         </is>
       </c>
+      <c r="N25" s="150">
+        <v>2021</v>
+      </c>
+      <c r="O25" s="150">
+        <v>2030</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
@@ -2573,20 +2710,20 @@
           <t xml:space="preserve">Portimão / Algarve</t>
         </is>
       </c>
-      <c r="D26" s="150"/>
-      <c r="E26" s="150">
+      <c r="D26" s="150">
         <v>9</v>
       </c>
+      <c r="E26" s="150"/>
       <c r="F26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G26" s="240"/>
+      <c r="G26" s="240">
+        <v>32.2</v>
+      </c>
       <c r="H26" s="240"/>
-      <c r="I26" s="240">
-        <v>32.2</v>
-      </c>
+      <c r="I26" s="240"/>
       <c r="J26" s="240">
         <v>33.81</v>
       </c>
@@ -2600,13 +2737,19 @@
           <t xml:space="preserve">A two-year 2027-28 return at ~$33M built from state outlay of ~€27M/yr, not a published F1 fee. The government declined to disclose the exact fee; the promoter says ticket revenue cannot cover it.</t>
         </is>
       </c>
-      <c r="M26" s="30" t="inlineStr">
+      <c r="M26" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.ojogo.pt/modalidades/artigo/formula-1-de-volta-a-portugal-governo-faz-as-contas-aos-milhoes/18030826
 https://www.fia.com/en/latest/article/formula-1-reveals-calendar-for-2027-season-with-10-sprint-events.5J8ePLyjRuMyWEIDNUKgY4
 https://www.formula1.com/en/latest/article/formula-1-to-return-to-portugal-in-2027-and-2028.6kRRgAnvEoGiOkJMkzp1Cr</t>
         </is>
       </c>
+      <c r="N26" s="150">
+        <v>2027</v>
+      </c>
+      <c r="O26" s="150">
+        <v>2028</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
@@ -2624,20 +2767,20 @@
           <t xml:space="preserve">Istanbul Park</t>
         </is>
       </c>
-      <c r="D27" s="150"/>
-      <c r="E27" s="150">
+      <c r="D27" s="150">
         <v>17</v>
       </c>
+      <c r="E27" s="150"/>
       <c r="F27" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">TRADE</t>
         </is>
       </c>
-      <c r="G27" s="240"/>
+      <c r="G27" s="240">
+        <v>36.28</v>
+      </c>
       <c r="H27" s="240"/>
-      <c r="I27" s="240">
-        <v>36.28</v>
-      </c>
+      <c r="I27" s="240"/>
       <c r="J27" s="240">
         <v>38.1</v>
       </c>
@@ -2651,7 +2794,7 @@
           <t xml:space="preserve">Returns from 2027 on a five-year deal at ~$40M/yr implied by a ~$200M package. The $117.8M paid by the circuit operator for a 30-year concession is separate from the F1 fee.</t>
         </is>
       </c>
-      <c r="M27" s="30" t="inlineStr">
+      <c r="M27" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.abola.pt/noticias/turquia-paga-fortuna-para-regressar-a-formula-1-2026042714332598182
 https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar
@@ -2659,6 +2802,12 @@
 https://www.formula1.com/en/latest/article/formula-1-returns-to-turkeys-istanbul-park-from-2027-as-part-of-new-five-year-agreement.1I7OZGeDPoC6Vysv3iqadY</t>
         </is>
       </c>
+      <c r="N27" s="150">
+        <v>2027</v>
+      </c>
+      <c r="O27" s="150">
+        <v>2031</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
@@ -2678,35 +2827,33 @@
       </c>
       <c r="D28" s="150"/>
       <c r="E28" s="150"/>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRADE</t>
-        </is>
-      </c>
-      <c r="G28" s="240"/>
-      <c r="H28" s="240">
+      <c r="F28" s="6"/>
+      <c r="G28" s="240">
         <v>57.75</v>
       </c>
+      <c r="H28" s="240"/>
       <c r="I28" s="240"/>
       <c r="J28" s="240"/>
-      <c r="K28" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">One-off 2026 race at Sepang staged under Bahrain's promoter rights, with the full Bahrain fee applying and Gulf Air as title sponsor.</t>
-        </is>
-      </c>
+      <c r="K28" s="33"/>
       <c r="L28" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">Unusual structure: Bahrain's promoter holds the championship rights but the 2026 race runs at Sepang. The file carries the full Bahrain fee (~$55-58M) with Bahrain branding and Gulf Air as title sponsor. One-off.</t>
         </is>
       </c>
-      <c r="M28" s="30" t="inlineStr">
+      <c r="M28" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.fia.com/news/fia-and-formula-1-announce-2026-calendar</t>
         </is>
       </c>
+      <c r="N28" s="150">
+        <v>2026</v>
+      </c>
+      <c r="O28" s="150">
+        <v>2026</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Italy</t>
         </is>
@@ -2723,22 +2870,14 @@
       </c>
       <c r="D29" s="151"/>
       <c r="E29" s="151"/>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRADE</t>
-        </is>
-      </c>
+      <c r="F29" s="7"/>
       <c r="G29" s="241">
         <v>28</v>
       </c>
       <c r="H29" s="241"/>
       <c r="I29" s="241"/>
       <c r="J29" s="241"/>
-      <c r="K29" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fee of about $28M per year for the Emilia Romagna race, which leaves the calendar after 2025.</t>
-        </is>
-      </c>
+      <c r="K29" s="34"/>
       <c r="L29" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">Off the calendar from 2026 (Madrid took the slot) and carried only for FY24-25. FY23 is deliberately blank because the 2023 race was cancelled by flooding under force majeure.</t>
@@ -2748,6 +2887,2126 @@
         <is>
           <t xml:space="preserve">https://racingnews365.com/f1-2025-circuit-contracts
 https://www.planetf1.com/features/imola-f1-future-calendar-21-million-emilia-romagna-grand-prix</t>
+        </is>
+      </c>
+      <c r="N29" s="150">
+        <v>2023</v>
+      </c>
+      <c r="O29" s="150">
+        <v>2025</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="20.00" customWidth="1"/>
+    <col min="2" max="2" width="30.00" customWidth="1"/>
+    <col min="3" max="3" width="30.00" customWidth="1"/>
+    <col min="4" max="4" width="9.00" customWidth="1"/>
+    <col min="5" max="5" width="9.00" customWidth="1"/>
+    <col min="6" max="6" width="20.00" customWidth="1"/>
+    <col min="7" max="7" width="20.00" customWidth="1"/>
+    <col min="8" max="8" width="14.00" customWidth="1"/>
+    <col min="9" max="9" width="14.00" customWidth="1"/>
+    <col min="10" max="10" width="14.00" customWidth="1"/>
+    <col min="11" max="11" width="14.00" customWidth="1"/>
+    <col min="12" max="12" width="30.00" customWidth="1"/>
+    <col min="13" max="13" width="62.00" customWidth="1"/>
+    <col min="14" max="14" width="62.00" customWidth="1"/>
+    <col min="15" max="15" width="55.00" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Country</t>
+        </is>
+      </c>
+      <c r="B1" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Race</t>
+        </is>
+      </c>
+      <c r="C1" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venue</t>
+        </is>
+      </c>
+      <c r="D1" s="188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round 2026</t>
+        </is>
+      </c>
+      <c r="E1" s="188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round 2027</t>
+        </is>
+      </c>
+      <c r="F1" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Title Partner 2026</t>
+        </is>
+      </c>
+      <c r="G1" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Title Partner 2027</t>
+        </is>
+      </c>
+      <c r="H1" s="188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Est. Naming Fee 2025 (USD m)</t>
+        </is>
+      </c>
+      <c r="I1" s="188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Est. Naming Fee 2026 (USD m)</t>
+        </is>
+      </c>
+      <c r="J1" s="188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Est. Naming Fee 2027 (USD m)</t>
+        </is>
+      </c>
+      <c r="K1" s="188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Est. Naming Fee 2028 (USD m)</t>
+        </is>
+      </c>
+      <c r="L1" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rights Holder</t>
+        </is>
+      </c>
+      <c r="M1" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+      <c r="N1" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI Notes</t>
+        </is>
+      </c>
+      <c r="O1" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Australia</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Australian Grand Prix</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Albert Park, Melbourne</t>
+        </is>
+      </c>
+      <c r="D2" s="150">
+        <v>1</v>
+      </c>
+      <c r="E2" s="150">
+        <v>3</v>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qatar Airways</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moët &amp; Chandon</t>
+        </is>
+      </c>
+      <c r="H2" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I2" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="J2" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K2" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Promoter (AGPC) sells the race title; rotates annually</t>
+        </is>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Title rotates almost every year: Heineken 2022, Rolex 2023-24, Louis Vuitton 2025, Qatar Airways 2026, Moët &amp; Chandon 2027. Deal values are not published.</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Promoter-held inventory resold each year rather than one F1 global deal, which is why the brand changes annually. AGPC's statutory report shows sponsorship only in aggregate.</t>
+        </is>
+      </c>
+      <c r="O2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/australia
+https://www.formula1.com/en/racing/2027
+https://www.bizofspeed.com/p/moet-and-chandon-buys-the-2027-australian
+https://www.motogp.com.au/uploads/images/Australian-Grand-Prix-Corporation-2022-Annual-Report-20.12.2022.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chinese Grand Prix</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shanghai International Circuit</t>
+        </is>
+      </c>
+      <c r="D3" s="150">
+        <v>2</v>
+      </c>
+      <c r="E3" s="150">
+        <v>5</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heineken</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heineken</t>
+        </is>
+      </c>
+      <c r="H3" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I3" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="J3" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K3" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F1 commercial / promoter</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heineken holds the title for both 2026 and 2027. No fee disclosed.</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heineken is also an F1 global partner, so the Shanghai title may sit inside a wider package rather than a standalone race deal. Not confirmed either way.</t>
+        </is>
+      </c>
+      <c r="O3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/china
+https://www.formula1.com/en/racing/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japan</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japanese Grand Prix</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suzuka</t>
+        </is>
+      </c>
+      <c r="D4" s="150">
+        <v>3</v>
+      </c>
+      <c r="E4" s="150">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aramco</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lenovo</t>
+        </is>
+      </c>
+      <c r="H4" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I4" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="J4" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K4" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F1 commercial / promoter</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aramco titles the race in 2026; Lenovo takes the Japanese title in 2027. No fee disclosed.</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Title switches brand between the two years, so the 2027 slot was resold. Aramco also titles Hungary from 2027, suggesting a portfolio rotation rather than single-race deals.</t>
+        </is>
+      </c>
+      <c r="O4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/japan
+https://www.formula1.com/en/racing/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bahrain</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bahrain Grand Prix</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sakhir (2026: Sepang, Malaysia)</t>
+        </is>
+      </c>
+      <c r="D5" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not held</t>
+        </is>
+      </c>
+      <c r="E5" s="150">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gulf Air (2026 race run at Sepang)</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gulf Air</t>
+        </is>
+      </c>
+      <c r="H5" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I5" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="J5" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K5" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F1 commercial / promoter</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The April 2026 round was cancelled; the race returned as a one-off at Sepang in October 2026, still badged Gulf Air Bahrain. Gulf Air holds the title again in 2027.</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gulf Air is a Bahrain state-linked carrier, so the title sits with the promoter rather than being sold to a third party. No value disclosed in any source opened.</t>
+        </is>
+      </c>
+      <c r="O5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/bahrain
+https://www.formula1.com/en/latest/article/formula-1-gulf-air-bahrain-grand-prix-in-malaysia-2026.1IHoy7D2dfCIugb5mH78cE
+https://www.formula1.com/en/racing/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saudi Arabian Grand Prix</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jeddah Corniche</t>
+        </is>
+      </c>
+      <c r="D6" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cancelled</t>
+        </is>
+      </c>
+      <c r="E6" s="150">
+        <v>2</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a (round cancelled)</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STC</t>
+        </is>
+      </c>
+      <c r="H6" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I6" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="J6" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K6" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F1 commercial / promoter</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 2026 round was cancelled in March and not replaced. STC holds the title for the 2027 return.</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One of two 2026 rounds not run. The 2027 title is confirmed by F1's calendar page; no fee published.</t>
+        </is>
+      </c>
+      <c r="O6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/saudi-arabia
+https://www.formula1.com/en/racing/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Miami Grand Prix</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Miami International Autodrome</t>
+        </is>
+      </c>
+      <c r="D7" s="150">
+        <v>4</v>
+      </c>
+      <c r="E7" s="150">
+        <v>6</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Crypto.com</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hard Rock</t>
+        </is>
+      </c>
+      <c r="H7" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I7" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="J7" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K7" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Promoter (South Florida Motorsports), co-promoted with F1</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Crypto.com titles the race through 2026; Hard Rock takes naming rights from 2027 for the Formula 1 Hard Rock Miami Grand Prix. No fee disclosed.</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The only documented title change on the 2027 calendar. Crypto.com's F1 deal was reported at roughly $100M over five years, but that was a global partnership including the Miami title, not a separable race fee.</t>
+        </is>
+      </c>
+      <c r="O7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/miami
+https://www.formula1.com/en/racing/2027
+https://f1miamigp.com/news/press-release/hard-rock-named-f1-miami-grand-prix-title-partner/
+https://www.cnbc.com/2021/06/29/formula-1-strikes-100-million-cryptocurrency-sponsorship.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canada</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canadian Grand Prix</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Circuit Gilles Villeneuve</t>
+        </is>
+      </c>
+      <c r="D8" s="150">
+        <v>5</v>
+      </c>
+      <c r="E8" s="150">
+        <v>7</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lenovo</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AWS</t>
+        </is>
+      </c>
+      <c r="H8" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I8" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="J8" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K8" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F1 commercial / promoter</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lenovo titles the Canadian race in 2026; AWS takes over for 2027. No fee disclosed.</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lenovo also titles Austria in 2026 and Japan and Spain in 2027, so its spend is spread across a portfolio of races rather than one.</t>
+        </is>
+      </c>
+      <c r="O8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/canada
+https://www.formula1.com/en/racing/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monaco</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monaco Grand Prix</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Circuit de Monaco</t>
+        </is>
+      </c>
+      <c r="D9" s="150">
+        <v>6</v>
+      </c>
+      <c r="E9" s="150">
+        <v>8</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Louis Vuitton</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Louis Vuitton</t>
+        </is>
+      </c>
+      <c r="H9" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I9" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="J9" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K9" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automobile Club de Monaco (promoter)</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Louis Vuitton is title partner in both years, having taken over the naming from TAG Heuer for 2026. No fee disclosed.</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LVMH has both the F1 global partnership and this title, so the Monaco naming is likely bundled. Neither the ACM release nor F1 publishes a value.</t>
+        </is>
+      </c>
+      <c r="O9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/monaco
+https://www.formula1.com/en/racing/2027
+https://acm.mc/en/louis-vuitton-becomes-title-partner-of-the-monaco-grand-prix-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spain</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Barcelona-Catalunya Grand Prix</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Circuit de Barcelona-Catalunya</t>
+        </is>
+      </c>
+      <c r="D10" s="150">
+        <v>7</v>
+      </c>
+      <c r="E10" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No (alternates with Belgium)</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSC Cruises</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="H10" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I10" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="J10" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="K10" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Circuit de Barcelona-Catalunya (promoter)</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Runs in 2026 under the MSC Cruises title. From 2027 the slot alternates year-on-year with Belgium. No fee disclosed.</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your Race_Promo_Calendar lists this race as ending in 2026; it returns on the alternate-year rotation. MSC also titles Austin, Sao Paulo, Portugal and Turkiye, so the releases treat these as one package.</t>
+        </is>
+      </c>
+      <c r="O10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/barcelona-catalunya
+https://www.mscpressarea.com/en_US/press-releases/msc-cruises-serves-as-title-sponsor-for-austin-2025-grand-prix-tm-announces-conti/
+https://www.formula1.com/en/racing/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Austria</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Austrian Grand Prix</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Red Bull Ring</t>
+        </is>
+      </c>
+      <c r="D11" s="150">
+        <v>8</v>
+      </c>
+      <c r="E11" s="150">
+        <v>11</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lenovo</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qatar Airways</t>
+        </is>
+      </c>
+      <c r="H11" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I11" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="J11" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K11" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Red Bull Ring (promoter)</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lenovo titles the 2026 race; Qatar Airways takes the Austrian naming for 2027. No fee disclosed.</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qatar Airways titles four races across the two years (Australia 2026, Austria and Azerbaijan and Qatar 2027), the widest single-brand spread in the file.</t>
+        </is>
+      </c>
+      <c r="O11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/austria
+https://www.formula1.com/en/racing/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United Kingdom</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">British Grand Prix</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Silverstone</t>
+        </is>
+      </c>
+      <c r="D12" s="150">
+        <v>9</v>
+      </c>
+      <c r="E12" s="150">
+        <v>10</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pirelli</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tag Heuer</t>
+        </is>
+      </c>
+      <c r="H12" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I12" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="J12" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K12" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRDC / Silverstone (promoter)</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pirelli titles the 2026 British Grand Prix; Tag Heuer takes the naming in 2027. No fee disclosed.</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRDC funds the race itself; the title sale is promoter inventory. Pirelli also titles Italy and the US race, so its spend is a multi-race package.</t>
+        </is>
+      </c>
+      <c r="O12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/great-britain
+https://www.formula1.com/en/racing/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Belgium</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Belgian Grand Prix</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spa-Francorchamps</t>
+        </is>
+      </c>
+      <c r="D13" s="150">
+        <v>10</v>
+      </c>
+      <c r="E13" s="150">
+        <v>12</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moët &amp; Chandon</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSC Cruises</t>
+        </is>
+      </c>
+      <c r="H13" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I13" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="J13" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K13" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Walloon government-backed promoter</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moët &amp; Chandon titles the race in 2026 and MSC Cruises in 2027. The round alternates year-on-year with Barcelona-Catalunya from 2027. No fee disclosed.</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brand changes between the two years, so the Spa naming is resold rather than a standing contract.</t>
+        </is>
+      </c>
+      <c r="O13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/belgium
+https://www.formula1.com/en/racing/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hungary</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hungarian Grand Prix</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hungaroring</t>
+        </is>
+      </c>
+      <c r="D14" s="150">
+        <v>11</v>
+      </c>
+      <c r="E14" s="150">
+        <v>13</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AWS</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aramco</t>
+        </is>
+      </c>
+      <c r="H14" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I14" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="J14" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K14" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hungaroring (state-supported promoter)</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AWS titles the 2026 race; Aramco takes the naming for 2027. No fee disclosed.</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Hungarian state discloses the race promotion fee in its gazette, but not the title sponsorship value.</t>
+        </is>
+      </c>
+      <c r="O14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/hungary
+https://www.formula1.com/en/racing/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Netherlands</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dutch Grand Prix</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Circuit Zandvoort</t>
+        </is>
+      </c>
+      <c r="D15" s="150">
+        <v>12</v>
+      </c>
+      <c r="E15" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not held</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heineken</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="H15" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I15" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="J15" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="K15" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dutch GP promoter</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 2026 race is the last under the current contract; the round is not on the 2027 calendar. Heineken holds the title. No fee disclosed.</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heineken is the obvious title holder given its Dutch base and its F1 global partnership, so this is unlikely to be a separately priced sale.</t>
+        </is>
+      </c>
+      <c r="O15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/netherlands
+https://www.formula1.com/en/racing/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Italy</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Italian Grand Prix</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monza</t>
+        </is>
+      </c>
+      <c r="D16" s="150">
+        <v>13</v>
+      </c>
+      <c r="E16" s="150">
+        <v>14</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pirelli</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pirelli</t>
+        </is>
+      </c>
+      <c r="H16" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I16" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="J16" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K16" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACI / SIAS (promoter)</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pirelli titles the race in both years. No fee disclosed.</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pirelli is the sole tyre supplier, so the Monza title is bundled into its wider F1 relationship rather than sold at a market rate.</t>
+        </is>
+      </c>
+      <c r="O16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/italy
+https://www.formula1.com/en/racing/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spain</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spanish Grand Prix (Madrid)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Madring / IFEMA</t>
+        </is>
+      </c>
+      <c r="D17" s="150">
+        <v>14</v>
+      </c>
+      <c r="E17" s="150">
+        <v>15</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tag Heuer</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lenovo</t>
+        </is>
+      </c>
+      <c r="H17" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I17" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="J17" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K17" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IFEMA Madrid (promoter)</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tag Heuer titles the first Madrid race in 2026; Lenovo takes the naming in 2027. No fee disclosed.</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tag Heuer moves from Monaco (2025) to Madrid (2026) then to Silverstone (2027), consistent with short, rotating title commitments rather than long contracts.</t>
+        </is>
+      </c>
+      <c r="O17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/spain
+https://www.formula1.com/en/racing/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Azerbaijan</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Azerbaijan Grand Prix</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baku City Circuit</t>
+        </is>
+      </c>
+      <c r="D18" s="150">
+        <v>15</v>
+      </c>
+      <c r="E18" s="150">
+        <v>16</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qatar Airways</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qatar Airways</t>
+        </is>
+      </c>
+      <c r="H18" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I18" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="J18" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K18" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baku City Circuit (state-backed promoter)</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qatar Airways titles the race in both years. No fee disclosed.</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One of the few titles held by the same brand in both 2026 and 2027, alongside Heineken at China, Louis Vuitton at Monaco, Pirelli at Italy, Qatar Airways at Qatar and Etihad at Abu Dhabi.</t>
+        </is>
+      </c>
+      <c r="O18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/azerbaijan
+https://www.formula1.com/en/racing/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Singapore</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Singapore Grand Prix</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marina Bay</t>
+        </is>
+      </c>
+      <c r="D19" s="150">
+        <v>16</v>
+      </c>
+      <c r="E19" s="150">
+        <v>18</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Singapore Airlines</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Singapore Airlines</t>
+        </is>
+      </c>
+      <c r="H19" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I19" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="J19" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K19" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Singapore GP Pte Ltd (promoter)</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Singapore Airlines titles the race in both years. No fee disclosed.</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SportsPro's report of the original deal states no financial details were revealed. Any value would sit in Singapore GP Pte Ltd accounts or STB disclosures, neither of which I retrieved.</t>
+        </is>
+      </c>
+      <c r="O19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/singapore
+https://www.formula1.com/en/racing/2027
+https://www.sportspro.com/sponsorship-marketing/sponsorship/singapore_airlines_replaces_singtel_as_gp_sponsor/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States Grand Prix</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Circuit of the Americas</t>
+        </is>
+      </c>
+      <c r="D20" s="150">
+        <v>17</v>
+      </c>
+      <c r="E20" s="150">
+        <v>19</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSC Cruises</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pirelli</t>
+        </is>
+      </c>
+      <c r="H20" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I20" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="J20" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K20" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Circuit of the Americas (promoter)</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSC Cruises titles the 2026 race at COTA; Pirelli takes the naming in 2027. No fee disclosed.</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSC's release covering Austin, Barcelona and Sao Paulo states no value for any of the three.</t>
+        </is>
+      </c>
+      <c r="O20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/united-states
+https://www.formula1.com/en/racing/2027
+https://www.mscpressarea.com/en_US/press-releases/msc-cruises-serves-as-title-sponsor-for-austin-2025-grand-prix-tm-announces-conti/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mexico</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mexico City Grand Prix</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autódromo Hermanos Rodríguez</t>
+        </is>
+      </c>
+      <c r="D21" s="150">
+        <v>18</v>
+      </c>
+      <c r="E21" s="150">
+        <v>20</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+      <c r="H21" s="150">
+        <v>0</v>
+      </c>
+      <c r="I21" s="150">
+        <v>0</v>
+      </c>
+      <c r="J21" s="150">
+        <v>0</v>
+      </c>
+      <c r="K21" s="150">
+        <v>0</v>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CIE (promoter)</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Runs without a title partner in both 2026 and 2027; the official name is simply Gran Premio de la Ciudad de México.</t>
+        </is>
+      </c>
+      <c r="N21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The only round with no naming sponsor in either year, which makes the zero a fact rather than a missing value. Worth flagging as an unsold slot.</t>
+        </is>
+      </c>
+      <c r="O21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/mexico
+https://www.formula1.com/en/racing/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brazil</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">São Paulo Grand Prix</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interlagos</t>
+        </is>
+      </c>
+      <c r="D22" s="150">
+        <v>19</v>
+      </c>
+      <c r="E22" s="150">
+        <v>21</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSC Cruises</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heineken</t>
+        </is>
+      </c>
+      <c r="H22" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I22" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="J22" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K22" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">São Paulo city government (promoter)</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSC Cruises titles the 2026 race; Heineken takes the naming for 2027. No fee disclosed.</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Title changes brand between years. MSC's package across Brazil, Austin, Barcelona, Portugal and Turkiye is the largest single-brand race-title footprint in the file.</t>
+        </is>
+      </c>
+      <c r="O22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/brazil
+https://www.formula1.com/en/racing/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Las Vegas Grand Prix</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Las Vegas Strip Circuit</t>
+        </is>
+      </c>
+      <c r="D23" s="150">
+        <v>20</v>
+      </c>
+      <c r="E23" s="150">
+        <v>22</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heineken</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heineken</t>
+        </is>
+      </c>
+      <c r="H23" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I23" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="J23" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K23" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F1 promotes directly (Liberty)</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heineken titles the race in both years. No fee disclosed.</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The only race F1 promotes itself, so the title revenue accrues to Liberty rather than a third-party promoter. No value disclosed.</t>
+        </is>
+      </c>
+      <c r="O23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/las-vegas
+https://www.formula1.com/en/racing/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qatar</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qatar Grand Prix</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lusail</t>
+        </is>
+      </c>
+      <c r="D24" s="150">
+        <v>21</v>
+      </c>
+      <c r="E24" s="150">
+        <v>23</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qatar Airways</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qatar Airways</t>
+        </is>
+      </c>
+      <c r="H24" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I24" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="J24" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K24" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qatar state-backed promoter</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qatar Airways titles the race in both years. No fee disclosed.</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">State-owned carrier and state-backed promoter on both sides of the deal, so there is no arm's-length price to disclose.</t>
+        </is>
+      </c>
+      <c r="O24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/qatar
+https://www.formula1.com/en/racing/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abu Dhabi Grand Prix</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yas Marina</t>
+        </is>
+      </c>
+      <c r="D25" s="150">
+        <v>22</v>
+      </c>
+      <c r="E25" s="150">
+        <v>24</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Etihad Airways</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Etihad Airways</t>
+        </is>
+      </c>
+      <c r="H25" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="I25" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="J25" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K25" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abu Dhabi state-backed promoter</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Etihad Airways titles the race in both years. No fee disclosed.</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As with Qatar, the airline and promoter are both state-linked. F1's calendar page uses the /united-arab-emirates slug rather than /abu-dhabi.</t>
+        </is>
+      </c>
+      <c r="O25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026/united-arab-emirates
+https://www.formula1.com/en/racing/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Portugal</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Portuguese Grand Prix (2027-28)</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Portimão / Algarve</t>
+        </is>
+      </c>
+      <c r="D26" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not held</t>
+        </is>
+      </c>
+      <c r="E26" s="150">
+        <v>9</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSC Cruises</t>
+        </is>
+      </c>
+      <c r="H26" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="I26" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="J26" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K26" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parkalgar / state-supported promoter</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Returns for 2027 and 2028, titled by MSC Cruises. No fee disclosed.</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New round with the title pre-sold to MSC before the first running. The Portuguese state's staging contribution is a separate payment to F1, not the naming fee.</t>
+        </is>
+      </c>
+      <c r="O26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turkey</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turkish Grand Prix (from 2027)</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Istanbul Park</t>
+        </is>
+      </c>
+      <c r="D27" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not held</t>
+        </is>
+      </c>
+      <c r="E27" s="150">
+        <v>17</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSC Cruises</t>
+        </is>
+      </c>
+      <c r="H27" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="I27" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="J27" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="K27" s="150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not disclosed</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Istanbul Park operator (concession)</t>
+        </is>
+      </c>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Returns from 2027 on a five-year agreement, titled by MSC Cruises. No fee disclosed.</t>
+        </is>
+      </c>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The reported ~$200M five-year package is the race promotion fee, not the naming deal. The $117.8M concession payment is separate again.</t>
+        </is>
+      </c>
+      <c r="O27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2027
+https://www.abola.pt/noticias/turquia-paga-fortuna-para-regressar-a-formula-1-2026042714332598182</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Italy</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emilia Romagna Grand Prix</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Imola</t>
+        </is>
+      </c>
+      <c r="D28" s="151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not held</t>
+        </is>
+      </c>
+      <c r="E28" s="151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not held</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="H28" s="151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="I28" s="151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="J28" s="151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="K28" s="151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Off the calendar from 2026; no title partner in either year.</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carried only for completeness against the Race_Promo_Calendar sheet. No 2026 or 2027 running means no naming deal.</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.formula1.com/en/racing/2026</t>
         </is>
       </c>
     </row>

--- a/RacePromo.xlsx
+++ b/RacePromo.xlsx
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="N2" s="150">
-        <v>2025</v>
+        <v>1985</v>
       </c>
       <c r="O2" s="150">
-        <v>2037</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="3">
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="N3" s="150">
-        <v>2025</v>
+        <v>2004</v>
       </c>
       <c r="O3" s="150">
         <v>2030</v>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="N4" s="150">
-        <v>2025</v>
+        <v>1976</v>
       </c>
       <c r="O4" s="150">
         <v>2029</v>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="N5" s="150">
-        <v>2022</v>
+        <v>2004</v>
       </c>
       <c r="O5" s="150">
         <v>2036</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="N8" s="150">
-        <v>2025</v>
+        <v>1967</v>
       </c>
       <c r="O8" s="150">
         <v>2035</v>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="N9" s="150">
-        <v>2026</v>
+        <v>1950</v>
       </c>
       <c r="O9" s="150">
         <v>2035</v>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="N10" s="150">
-        <v>2023</v>
+        <v>1991</v>
       </c>
       <c r="O10" s="150">
         <v>2032</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="N11" s="150">
-        <v>2025</v>
+        <v>1964</v>
       </c>
       <c r="O11" s="150">
         <v>2041</v>
@@ -1880,7 +1880,7 @@
         </is>
       </c>
       <c r="N12" s="150">
-        <v>2025</v>
+        <v>1950</v>
       </c>
       <c r="O12" s="150">
         <v>2034</v>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="N13" s="150">
-        <v>2026</v>
+        <v>1950</v>
       </c>
       <c r="O13" s="150">
         <v>2031</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="N14" s="150">
-        <v>2028</v>
+        <v>1986</v>
       </c>
       <c r="O14" s="150">
         <v>2032</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="N15" s="150">
-        <v>2021</v>
+        <v>1952</v>
       </c>
       <c r="O15" s="150">
         <v>2026</v>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="N16" s="150">
-        <v>2026</v>
+        <v>1950</v>
       </c>
       <c r="O16" s="150">
         <v>2031</v>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="N18" s="150">
-        <v>2027</v>
+        <v>2017</v>
       </c>
       <c r="O18" s="150">
         <v>2030</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="N19" s="150">
-        <v>2022</v>
+        <v>2008</v>
       </c>
       <c r="O19" s="150">
         <v>2028</v>
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="N20" s="150">
-        <v>2026</v>
+        <v>1959</v>
       </c>
       <c r="O20" s="150">
         <v>2034</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="N21" s="150">
-        <v>2026</v>
+        <v>1963</v>
       </c>
       <c r="O21" s="150">
         <v>2028</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="N22" s="150">
-        <v>2023</v>
+        <v>1973</v>
       </c>
       <c r="O22" s="150">
         <v>2030</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="N24" s="150">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="O24" s="150">
         <v>2032</v>
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="N25" s="150">
-        <v>2021</v>
+        <v>2009</v>
       </c>
       <c r="O25" s="150">
         <v>2030</v>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="N26" s="150">
-        <v>2027</v>
+        <v>2020</v>
       </c>
       <c r="O26" s="150">
         <v>2028</v>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="N27" s="150">
-        <v>2027</v>
+        <v>2005</v>
       </c>
       <c r="O27" s="150">
         <v>2031</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="N28" s="150">
-        <v>2026</v>
+        <v>1999</v>
       </c>
       <c r="O28" s="150">
         <v>2026</v>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="N29" s="150">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="O29" s="150">
         <v>2025</v>
